--- a/results/result_evaluation_logs/D_System_Simplification.xlsx
+++ b/results/result_evaluation_logs/D_System_Simplification.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -623,11 +618,6 @@
 wd:Q25095540 wd:P31 wd:Q482994 .
 wd:Q25095540 wd:P175 wd:Q364841 .
 wd:Q25095540 wd:P264 wd:Q1516254 .</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5fa5b699-5035-4f9d-bcdb-e513bfa739b5</t>
         </is>
       </c>
     </row>
@@ -710,11 +700,6 @@
 wd:Q20992419 wd:P931 wd:Q160 .</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>82514d02-6ae5-4306-a61f-9cf0b8300621</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -788,11 +773,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q466774 wd:P108 wd:Q273626 .
 wd:Q466774 wd:P184 wd:Q370496 .</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>f34e5465-14de-4f51-b324-534706154144</t>
         </is>
       </c>
     </row>
@@ -872,11 +852,6 @@
 wd:Q72697912 wd:P166 wd:Q4557532 .</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>cbb4b599-a0d9-426d-ac8e-71caf81b13a4</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -949,11 +924,6 @@
         <is>
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q36771 wd:P569 wd:Q29999 .</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>e601f514-6f6e-4853-8730-12b696e190f0</t>
         </is>
       </c>
     </row>
@@ -1031,11 +1001,6 @@
 wd:Q506252 wd:P366 wd:Q177 .</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>836501af-cbac-4d18-801c-b34c8e88f44a</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1109,11 +1074,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2226643 wd:P31 wd:Q65943 .
 wd:Q2226643 wd:P138 wd:Q28937 .</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>437c445e-e94e-482e-96e0-e01daa1762e6</t>
         </is>
       </c>
     </row>
@@ -1198,11 +1158,6 @@
 wd:Q2601034 wd:P577 wd:Q3939773 .</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>93f8a9b4-7a21-4c46-8c90-8eb7b9ab17bf</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1248,10 +1203,10 @@
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -1291,11 +1246,6 @@
 wd:Q7838 wd:P37 wd:Q924 .</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>c53a9dcf-251f-4fce-8939-66083f02ee8a</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1371,11 +1321,6 @@
 wd:Q85563 wd:P3373 wd:Q91204 .</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2cc25585-735d-4d1f-ad68-9c3c206585ea</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1452,11 +1397,6 @@
 wd:Q5395743 wd:P1412 wd:Q1321 .</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6703191a-105c-4b47-abc4-742bd401f6d1</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1532,11 +1472,6 @@
 wd:Q516760 wd:P276 wd:Q1605654 .</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>e1457836-9f3d-4fbc-a701-9d2bf0fc803d</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1612,11 +1547,6 @@
 wd:Q3561541 wd:P200 wd:Q5364109 .</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>4aa1e8b2-0ff1-43ca-92db-f15d2cd72658</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1632,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1641,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1650,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1671,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1680,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1746,11 +1676,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>b67668c5-54e2-4bef-870d-06b2ed2331ee</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1825,11 +1750,6 @@
 wd:Q3311362 wd:P131 wd:Q66117 .</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>35165ede-cb43-472b-b013-2dd3dc31e50b</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1903,11 +1823,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q7044514 wd:P31 wd:Q46046 .
 wd:Q7044514 wd:P175 wd:Q234199 .</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>fd9528bb-99b1-4621-80dc-32b5852a8e43</t>
         </is>
       </c>
     </row>
@@ -1987,11 +1902,6 @@
 wd:Q6933370 wd:P31 wd:Q607380 .
 wd:Q607380 wd:P453 wd:Q6933370 .
 wd:Q6933370 wd:P31 wd:Q607380 .</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2a11170b-f431-4bea-bb92-68613ed49167</t>
         </is>
       </c>
     </row>
@@ -2074,11 +1984,6 @@
 wd:Q928828 wd:P131 wd:Q794 .</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>6f3bb742-56e2-4042-9048-288083a29ac2</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2153,11 +2058,6 @@
 wd:Q20671544 wd:P106 wd:Q638 .
 wd:Q20671544 wd:P412 wd:Q27914 .
 wd:Q20671544 wd:P527 wd:Q27914 .</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>53451be4-89e9-4404-9397-97685d91bf4e</t>
         </is>
       </c>
     </row>
@@ -2240,11 +2140,6 @@
 wd:Q3048624 wd:P1412 "English" .</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>e547e62e-5d59-4ad2-ae82-8ea44bd1f375</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2323,11 +2218,6 @@
 wd:Q17052475 wd:P1012 wd:Q395 .</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>226ef3d5-43b8-4192-a207-0971bfe83a3d</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2404,11 +2294,6 @@
 wd:Q18036690 wd:P703 wd:Q15978631 .</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>e5a39d92-3034-4d94-96c2-d5552b55e483</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2484,11 +2369,6 @@
 wd:Q188197 wd:P1346 wd:Q674962 .</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>c06ae65c-746d-4b90-b8ce-8299b5bb0bd5</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2563,11 +2443,6 @@
 wd:Q5554167 wd:P162 wd:Q16239205 .
 wd:Q5554167 wd:P1037 wd:Q220072 .
 wd:Q5554167 wd:P161 wd:Q520445 .</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>1ae194c0-6556-4127-9be9-d82c0d39f97f</t>
         </is>
       </c>
     </row>
@@ -2654,11 +2529,6 @@
 wd:Q62066211 wd:P1050 wd:Q683302 .</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>960fea77-5ccb-46f7-8522-d37f8ca4faed</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2734,11 +2604,6 @@
 wd:Q5546527 wd:P138 wd:Q8229 .</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>e001406b-a75f-4a50-9b39-2e7baa48a5d8</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2813,11 +2678,6 @@
 wd:Q22082365 wd:P131 wd:Q965 .
 wd:Q965 wd:P463 wd:Q47543 .
 wd:Q22082365 wd:P31 wd:Q484170 .</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>ffdc1c59-0331-4028-8a73-69340a9e2b2b</t>
         </is>
       </c>
     </row>
@@ -2901,11 +2761,6 @@
 wd:Q685 wd:P131 wd:Q408 .</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>e486f30c-30f6-4331-940b-6576958ba7c0</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2951,10 +2806,10 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>5</v>
@@ -2994,11 +2849,6 @@
 wd:Q179163 wd:P361 wd:Q54152 .</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>f749776e-d33f-4c06-9390-edcb4cb06b0a</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3044,10 +2894,10 @@
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
@@ -3081,11 +2931,6 @@
 wd:Q14707624 wd:P607 wd:Q30 .</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>4d27e61d-a399-4ea2-b048-7adbb2a9bbba</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3159,11 +3004,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q64876878 wd:P674 wd:Q65090308 .
 wd:Q64876878 wd:P725 wd:Q262170 .</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>add52d83-170f-4961-a57c-1edba9cbfdbb</t>
         </is>
       </c>
     </row>
@@ -3241,11 +3081,6 @@
 wd:Q1088790 wd:P150 wd:Q190518 .
 wd:Q190518 wd:P150 wd:Q28 .
 wd:Q1240173 wd:P131 wd:Q190518 .</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>f3a8b3e7-e92b-42ec-a309-d821c9ec0d30</t>
         </is>
       </c>
     </row>
@@ -3327,11 +3162,6 @@
 &lt;http://example.org/movie/The_Dreamers&gt; &lt;http://example.org/relationship/features&gt; &lt;http://example.org/person/Gilbert_Adair&gt; .</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>96af26bf-056c-4444-996e-8861425c8da7</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3408,11 +3238,6 @@
 wd:Q41792848 wd:P106 wd:Q2515 .</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>72104f24-75bc-4499-bfc4-e5ccbf778325</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3488,11 +3313,6 @@
 wd:Q1490434 &lt;http://www.wikidata.org/entity/P1433&gt; wd:Q183 .</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>b578f0f0-2a18-43ed-acb4-a442210cee15</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3538,10 +3358,10 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
@@ -3567,11 +3387,6 @@
 wd:Q2616869 wd:P1433 wd:Q1126800 .
 wd:Q2616869 wd:P361 wd:Q1126800 .
 wd:Q2616869 wd:P1552 wd:Q132311 .</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>55440f7c-fda2-4549-aa69-c57ec4c6beed</t>
         </is>
       </c>
     </row>
@@ -3654,11 +3469,6 @@
 wd:Q1084560 wd:P361 wd:Q145 .</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>34226fe4-f6e0-453d-8e7e-1cd15542e68f</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3735,11 +3545,6 @@
 wd:Q183 wd:P179 wd:Q907827 .</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>1e065e32-5ac9-45e7-88ae-17a957362d6f</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3816,11 +3621,6 @@
 wd:Q1064344 wd:P1366 wd:Q1406 .</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>8fcfd490-b715-4d84-92ba-641283979d87</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3897,11 +3697,6 @@
 wd:Q47554 wd:P206 wd:Q1261531 .</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>59941a72-6567-47c7-97a4-e17a08e3b3e7</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3941,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -3982,11 +3777,6 @@
 wd:Q54322348 wd:P131 wd:Q121 .</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>56d84411-f015-47e5-bf83-d8426b8686a3</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4062,11 +3852,6 @@
 wd:Q87412161 wd:P31 wd:Q5 .</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>0616e621-7da9-41b1-bfba-0d78eb847370</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4142,11 +3927,6 @@
 wd:Q29644512 wd:P570 wd:Q28369 .</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>4d64ffbe-a61f-4f16-a933-534c6b37a4ac</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4162,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4171,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4180,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4201,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4210,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4233,11 +4013,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>8a4be7cd-87aa-4534-922c-97aaeda96e2a</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4314,11 +4089,6 @@
 wd:Q92560 wd:P31 wd:Q231302 .</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>878315c9-7be2-4b81-9cb4-8e9a7bbf7711</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4392,11 +4162,6 @@
           <t>@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q18036732 wd:P276 wd:Q753805 .
 wd:Q18036732 wd:P31 wd:Q7187 .</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>31015edc-c2b2-43e9-9169-8d15e8571a0c</t>
         </is>
       </c>
     </row>
@@ -4480,11 +4245,6 @@
 wd:Q979352 wd:P131 wd:Q1438 .</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>b2bca5e5-0a66-4308-9b8f-03d13255b628</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4563,11 +4323,6 @@
 wd:Q4546576 wd:P155 wd:Q190118 .</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1e7b7ee2-6b52-4ec1-ac65-4b9c7e443eab</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4644,11 +4399,6 @@
 wd:Q2822458 wd:P361 wd:Q1140115 .</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>e6a9437e-1caf-44df-a25f-d4f169da5596</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4723,11 +4473,6 @@
 wd:Q2362697 wd:P556 wd:Q503601 .
 wd:Q2362697 &lt;http://www.wikidata.org/prop/direct/P31&gt; wd:Q503601 .
 wd:Q503601 &lt;http://www.wikidata.org/prop/direct/P279&gt; wd:P556 .</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>1417d2f9-6853-4f19-9ac7-8a5620e449d0</t>
         </is>
       </c>
     </row>
